--- a/Hand_edited_log/7/StudentsSolution.xlsx
+++ b/Hand_edited_log/7/StudentsSolution.xlsx
@@ -82,109 +82,139 @@
     <x:t>6</x:t>
   </x:si>
   <x:si>
+    <x:t>hieplshe180170</x:t>
+  </x:si>
+  <x:si>
     <x:t>hieupmhe181979</x:t>
   </x:si>
   <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hungcnthe170248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
     <x:t>HungNPHE186981</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hungnthe172192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>huynqhe171567</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>huyvdhe173458</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khanhnthe181027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>kietpthe182092</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>minhvqhe180094</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>namnhhe161947</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>nghianthe181360</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>nguyenndhe186205</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>QuanNAHE180983</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>quocdkhe181519</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sonthhe186811</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>thangtdhe173186</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>23</x:t>
   </x:si>
   <x:si>
     <x:t>Tiennxhe181563</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>tienpqhe176483</x:t>
   </x:si>
   <x:si>
-    <x:t>20</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>tuanmahe182582</x:t>
   </x:si>
   <x:si>
-    <x:t>21</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>tunpthe187324</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>vannthe151384</x:t>
   </x:si>
   <x:si>
-    <x:t>23</x:t>
+    <x:t>28</x:t>
   </x:si>
   <x:si>
     <x:t>vinhnqhe187284</x:t>
   </x:si>
   <x:si>
-    <x:t>24</x:t>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>vutnhe186197</x:t>
@@ -558,7 +588,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G25"/>
+  <x:dimension ref="A1:G30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
@@ -1145,6 +1175,121 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
